--- a/docs/database/GPS_Data_Dictionary.xlsx
+++ b/docs/database/GPS_Data_Dictionary.xlsx
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>เวอร์ชัน: RBAC 6 Role / Schema 50 ตาราง / รวม Firmware Override รายเครื่อง [ใหม่]</t>
+          <t>เวอร์ชัน: RBAC 6 Role / Schema 49 ตาราง / รวม Firmware Override รายเครื่อง [ใหม่]</t>
         </is>
       </c>
     </row>
@@ -828,6 +828,20 @@
       <c r="A22" t="inlineStr">
         <is>
           <t>ปรับปรุงรอบ 2 (2026-08-28): เปลี่ยน Role กลับเป็นตารางจริง (ROLE) แทน Postgres enum เพราะ Admin ต้องสร้าง Role ใหม่ได้ผ่านหน้า User/Role Management (ยืนยันกับทีมแล้ว) — ROLE_PERMISSION ยังคงตัดตาราง PERMISSION (catalog) ออกเหมือนเดิม เก็บ resource/action ตรงกับ role_id ไปเลย ดูเหตุผลเต็มใน comment ของ backend/prisma/schema.prisma</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ปรับปรุงรอบ 3 (2026-08-28, รีวิวโดย kittiphong): ลบแถว PERMISSION -&gt; ROLE_PERMISSION ที่ค้างอยู่ในชีท "Relationships (ERD)" แถวที่ 13 ออก (ตกหล่นจากตอนตัดตาราง PERMISSION catalog — ที่อื่นทุกชีทตัดออกไปแล้วแต่ ERD ยังไม่ได้ตัด)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ปรับปรุงรอบ 4 (2026-08-28): แก้ A2 จาก "Schema 50 ตาราง" เป็น "Schema 49 ตาราง" ให้ตรงกับจำนวนที่นับจริงในแถว "รวมทั้งหมด" (ของเก่าที่ค้างมาก่อน ไม่เกี่ยวกับการเปลี่ยน Role table)</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14541,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
@@ -25374,7 +25387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -25650,7 +25663,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PERMISSION</t>
+          <t>USER</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -25660,19 +25673,19 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>ROLE_PERMISSION</t>
+          <t>AUDIT_LOG</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>creates</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>USER</t>
+          <t>CONFIG_SCOPE_LEVELS</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -25682,19 +25695,19 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>AUDIT_LOG</t>
+          <t>CONFIG_TEMPLATE</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>creates</t>
+          <t>scoped by</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>CONFIG_SCOPE_LEVELS</t>
+          <t>CONFIG_TEMPLATE</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -25704,19 +25717,19 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>CONFIG_TEMPLATE</t>
+          <t>CONFIG_TEMPLATE_VERSION</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>scoped by</t>
+          <t>has versions</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>CONFIG_TEMPLATE</t>
+          <t>DEVICE</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -25726,19 +25739,19 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>CONFIG_TEMPLATE_VERSION</t>
+          <t>DEVICE_CONFIG</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>has versions</t>
+          <t>has</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>DEVICE</t>
+          <t>CONFIG_TEMPLATE_VERSION</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -25753,14 +25766,14 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>applied as</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>CONFIG_TEMPLATE_VERSION</t>
+          <t>DEVICE_CONFIG</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -25770,19 +25783,19 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>DEVICE_CONFIG</t>
+          <t>CONFIG_HISTORY</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>applied as</t>
+          <t>logs</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>DEVICE_CONFIG</t>
+          <t>DEVICE</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -25792,12 +25805,12 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>CONFIG_HISTORY</t>
+          <t>DEVICE_CONFIG_SNAPSHOTS</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>logs</t>
+          <t>snapshotted</t>
         </is>
       </c>
     </row>
@@ -25814,19 +25827,19 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>DEVICE_CONFIG_SNAPSHOTS</t>
+          <t>DEVICE_CONFIG_OVERRIDE</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>snapshotted</t>
+          <t>overridden at field</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>DEVICE</t>
+          <t>CONFIG_DEFINITION</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -25841,36 +25854,36 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>overridden at field</t>
+          <t>limited to field_overridable=true</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>CONFIG_DEFINITION</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>CONFIG_TEMPLATE</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>1 : N</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>DEVICE_CONFIG_OVERRIDE</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>limited to field_overridable=true</t>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>CONFIG_CHANGE_REQUEST</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>proposed change to  [ใหม่]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>CONFIG_TEMPLATE</t>
+          <t>CONFIG_DEFINITION</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -25885,14 +25898,14 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>proposed change to  [ใหม่]</t>
+          <t>targets field  [ใหม่]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>CONFIG_DEFINITION</t>
+          <t>USER</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -25907,14 +25920,14 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>targets field  [ใหม่]</t>
+          <t>requested by (Senior Technician)  [ใหม่]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>USER</t>
+          <t>CONFIG_TEMPLATE_VERSION</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -25929,29 +25942,29 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>requested by (Senior Technician)  [ใหม่]</t>
+          <t>converted into (if accepted)  [ใหม่]</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>CONFIG_TEMPLATE_VERSION</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>FIRMWARE</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>1 : N</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>CONFIG_CHANGE_REQUEST</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>converted into (if accepted)  [ใหม่]</t>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>FIRMWARE_FILES</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>has builds</t>
         </is>
       </c>
     </row>
@@ -25968,19 +25981,19 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>FIRMWARE_FILES</t>
+          <t>FIRMWARE_COMPATIBILITY</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>has builds</t>
+          <t>compatible with</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>FIRMWARE</t>
+          <t>HARDWARE_REVISION</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -25995,14 +26008,14 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>compatible with</t>
+          <t>supports</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>HARDWARE_REVISION</t>
+          <t>DEVICE</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -26012,41 +26025,41 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>FIRMWARE_COMPATIBILITY</t>
+          <t>DEVICE_FIRMWARE_PARTITIONS</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>supports</t>
+          <t>has</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>DEVICE</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>1 : N</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>DEVICE_FIRMWARE_PARTITIONS</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>has</t>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>FIRMWARE_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>installed at field  [ใหม่]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>DEVICE</t>
+          <t>FIRMWARE</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -26061,29 +26074,29 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>installed at field  [ใหม่]</t>
+          <t>limited to installable_by_technician=true (unless Senior Technician)  [ใหม่]</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>FIRMWARE</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>DEPLOYMENT_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>1 : N</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>FIRMWARE_OVERRIDE</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>limited to installable_by_technician=true (unless Senior Technician)  [ใหม่]</t>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_BATCHES</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>splits into</t>
         </is>
       </c>
     </row>
@@ -26100,19 +26113,19 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BATCHES</t>
+          <t>CAMPAIGN_TARGET</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>splits into</t>
+          <t>targets</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>DEPLOYMENT_CAMPAIGN</t>
+          <t>CAMPAIGN_BATCHES</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -26127,14 +26140,14 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>targets</t>
+          <t>groups</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BATCHES</t>
+          <t>DEPLOYMENT_CAMPAIGN</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -26144,19 +26157,19 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>CAMPAIGN_TARGET</t>
+          <t>CAMPAIGN_ASSIGNMENT</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>assigns per customer</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>DEPLOYMENT_CAMPAIGN</t>
+          <t>CUSTOMER</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -26171,14 +26184,14 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>assigns per customer</t>
+          <t>scoped to</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>CUSTOMER</t>
+          <t>USER</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -26193,36 +26206,36 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>scoped to</t>
+          <t>assigned operation</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>1 : N</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>CAMPAIGN_ASSIGNMENT</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>assigned operation</t>
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_TARGET</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>0/1 : N</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>DEPLOYMENT_JOB</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>generates (source_type=CAMPAIGN)  [แก้ไข รอบที่ 8 — เดิมบังคับ 1:N]</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>CAMPAIGN_TARGET</t>
+          <t>DEVICE</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -26237,19 +26250,19 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>generates (source_type=CAMPAIGN)  [แก้ไข รอบที่ 8 — เดิมบังคับ 1:N]</t>
+          <t>generates directly (source_type=AD_HOC_OVERRIDE)  [ใหม่]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>DEVICE</t>
+          <t>FIRMWARE_OVERRIDE</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>0/1 : N</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -26259,36 +26272,36 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>generates directly (source_type=AD_HOC_OVERRIDE)  [ใหม่]</t>
+          <t>executed via  [ใหม่]</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>FIRMWARE_OVERRIDE</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>1 : 1</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>DEPLOYMENT_JOB</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>executed via  [ใหม่]</t>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>DEPLOYMENT_LOG</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>logs</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>DEPLOYMENT_JOB</t>
+          <t>INCIDENTS</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -26298,41 +26311,41 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>DEPLOYMENT_LOG</t>
+          <t>ROLLBACK_HISTORY</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>logs</t>
+          <t>triggers</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
+          <t>DETECTION_RULES</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
           <t>INCIDENTS</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>1 : N</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>ROLLBACK_HISTORY</t>
-        </is>
-      </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>triggers</t>
+          <t>detects</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>DETECTION_RULES</t>
+          <t>INCIDENTS</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -26342,41 +26355,41 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>INCIDENTS</t>
+          <t>INCIDENT_CORRELATIONS</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>detects</t>
+          <t>correlates</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
+          <t>DEPLOYMENT_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>1 : N</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
           <t>INCIDENTS</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>1 : N</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>INCIDENT_CORRELATIONS</t>
-        </is>
-      </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>correlates</t>
+          <t>linked to</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>DEPLOYMENT_CAMPAIGN</t>
+          <t>APPROVAL_CHAIN_DEFINITIONS</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -26386,19 +26399,19 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>INCIDENTS</t>
+          <t>APPROVAL_REQUESTS</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>linked to</t>
+          <t>defines</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>APPROVAL_CHAIN_DEFINITIONS</t>
+          <t>USER</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -26413,7 +26426,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>defines</t>
+          <t>requests</t>
         </is>
       </c>
     </row>
@@ -26435,7 +26448,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>chosen as approver</t>
         </is>
       </c>
     </row>
@@ -26452,19 +26465,19 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>APPROVAL_REQUESTS</t>
+          <t>DEVICE_GROUPS</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>chosen as approver</t>
+          <t>creates</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>USER</t>
+          <t>DEVICE_GROUPS</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -26474,19 +26487,19 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>DEVICE_GROUPS</t>
+          <t>DEVICE_GROUP_MEMBERS</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>creates</t>
+          <t>contains</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>DEVICE_GROUPS</t>
+          <t>DEVICE</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -26501,14 +26514,14 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>contains</t>
+          <t>member of</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>DEVICE</t>
+          <t>USER</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -26518,19 +26531,19 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>DEVICE_GROUP_MEMBERS</t>
+          <t>SAVED_SEARCHES</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>member of</t>
+          <t>owns</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>USER</t>
+          <t>DEVICE</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -26540,32 +26553,10 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>SAVED_SEARCHES</t>
+          <t>DEVICE_CUSTOM_FIELD_VALUES</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>owns</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>DEVICE</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>1 : N</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>DEVICE_CUSTOM_FIELD_VALUES</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>has</t>
         </is>

--- a/docs/database/GPS_Data_Dictionary.xlsx
+++ b/docs/database/GPS_Data_Dictionary.xlsx
@@ -622,6 +622,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -800,6 +801,8 @@
       </c>
       <c r="D14" s="4" t="n"/>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
@@ -821,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -14549,6 +14553,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="22">
       <c r="A3" s="21" t="inlineStr">
         <is>
@@ -14912,7 +14917,7 @@
       <c r="E18" s="26" t="n"/>
       <c r="F18" s="26" t="inlineStr">
         <is>
-          <t>ค่าคงที่อ้างอิงจากโค้ด (เดิมเคยเป็น Postgres enum): SW, Operation, ST, OT, Auditor, Admin,SuperAdmin — Role ใหม่ที่ Admin สร้างเพิ่มทีหลังตั้ง code เองได้อิสระ ไม่จำกัดแค่ 6 ค่านี้</t>
+          <t>ค่าคงที่อ้างอิงจากโค้ด (เดิมเคยเป็น Postgres enum): SW, Operation, ST, OT, Auditor, Admin, SuperAdmin — Role ใหม่ที่ Admin สร้างเพิ่มทีหลังตั้ง code เองได้อิสระ ไม่จำกัดแค่ 7 ค่านี้</t>
         </is>
       </c>
     </row>
